--- a/labor_ledger.xlsx
+++ b/labor_ledger.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Monthly Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Labor'!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Monthly Summary'!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Labor'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Monthly Summary'!$A$1:$B$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,14 +427,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
@@ -494,8 +494,44 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Oct 17, 2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HED LABOR</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1500</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:J2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -506,11 +542,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -525,8 +561,18 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1500</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1"/>
+  <autoFilter ref="A1:B2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>